--- a/4/FY3/FY3_optimization_results/top10_solutions.xlsx
+++ b/4/FY3/FY3_optimization_results/top10_solutions.xlsx
@@ -487,352 +487,352 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88</v>
+        <v>85.5</v>
       </c>
       <c r="B2" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="E2" t="n">
-        <v>6090.878289413313</v>
+        <v>6207.13201272151</v>
       </c>
       <c r="F2" t="n">
-        <v>-397.5862864422747</v>
+        <v>-368.1382389445425</v>
       </c>
       <c r="G2" t="n">
         <v>700</v>
       </c>
       <c r="H2" t="n">
-        <v>6108.188439777753</v>
+        <v>6243.380114947775</v>
       </c>
       <c r="I2" t="n">
-        <v>98.11156375919677</v>
+        <v>92.43756924016259</v>
       </c>
       <c r="J2" t="n">
-        <v>621.6</v>
+        <v>639.975</v>
       </c>
       <c r="K2" t="n">
-        <v>3.099999999999998</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74.5</v>
+        <v>76.5</v>
       </c>
       <c r="B3" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>6820.956291312405</v>
+        <v>6708.740124666529</v>
       </c>
       <c r="F3" t="n">
-        <v>-39.72724774311018</v>
+        <v>-47.88492167265395</v>
       </c>
       <c r="G3" t="n">
         <v>700</v>
       </c>
       <c r="H3" t="n">
-        <v>6855.162803450422</v>
+        <v>6739.554912695508</v>
       </c>
       <c r="I3" t="n">
-        <v>83.61745026759355</v>
+        <v>80.46790781983935</v>
       </c>
       <c r="J3" t="n">
         <v>695.1</v>
       </c>
       <c r="K3" t="n">
-        <v>3.099999999999998</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>77.5</v>
+        <v>81</v>
       </c>
       <c r="B4" t="n">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>6666.634010929357</v>
+        <v>6446.151094294739</v>
       </c>
       <c r="F4" t="n">
-        <v>6.991701929395276</v>
+        <v>-183.1128526226671</v>
       </c>
       <c r="G4" t="n">
         <v>700</v>
       </c>
       <c r="H4" t="n">
-        <v>6681.784783905024</v>
+        <v>6484.946841624716</v>
       </c>
       <c r="I4" t="n">
-        <v>75.33242242779062</v>
+        <v>61.83385584492706</v>
       </c>
       <c r="J4" t="n">
-        <v>698.775</v>
+        <v>680.4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.000000000000004</v>
+        <v>2.800000000000004</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74.5</v>
+        <v>81</v>
       </c>
       <c r="B5" t="n">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="C5" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="E5" t="n">
-        <v>6836.990593877101</v>
+        <v>6454.285686476831</v>
       </c>
       <c r="F5" t="n">
-        <v>18.09057944940696</v>
+        <v>-131.75305891172</v>
       </c>
       <c r="G5" t="n">
         <v>700</v>
       </c>
       <c r="H5" t="n">
-        <v>6852.49041968964</v>
+        <v>6485.259710554797</v>
       </c>
       <c r="I5" t="n">
-        <v>73.98114573550708</v>
+        <v>63.80923252611723</v>
       </c>
       <c r="J5" t="n">
-        <v>698.775</v>
+        <v>688.975</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>2.800000000000004</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>77.5</v>
+        <v>103.5</v>
       </c>
       <c r="B6" t="n">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="E6" t="n">
-        <v>6628.540638876251</v>
+        <v>5411.717683083119</v>
       </c>
       <c r="F6" t="n">
-        <v>-164.8363953237135</v>
+        <v>-549.6278005978547</v>
       </c>
       <c r="G6" t="n">
         <v>700</v>
       </c>
       <c r="H6" t="n">
-        <v>6685.68069695591</v>
+        <v>5257.643742938221</v>
       </c>
       <c r="I6" t="n">
-        <v>92.90575055594888</v>
+        <v>92.13634686461182</v>
       </c>
       <c r="J6" t="n">
-        <v>680.4</v>
+        <v>551.775</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>2.799999999999997</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>82</v>
+        <v>76.5</v>
       </c>
       <c r="B7" t="n">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="C7" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>6384.117758649781</v>
+        <v>6731.150879596696</v>
       </c>
       <c r="F7" t="n">
-        <v>-266.8601302732659</v>
+        <v>45.46259068552308</v>
       </c>
       <c r="G7" t="n">
         <v>700</v>
       </c>
       <c r="H7" t="n">
-        <v>6434.220074995405</v>
+        <v>6731.150879596696</v>
       </c>
       <c r="I7" t="n">
-        <v>89.63637447369945</v>
+        <v>45.46259068552308</v>
       </c>
       <c r="J7" t="n">
-        <v>655.9</v>
+        <v>700</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>2.700000000000003</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>74.5</v>
+        <v>76.5</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>6855.162803450422</v>
+        <v>6732.084661052119</v>
       </c>
       <c r="F8" t="n">
-        <v>83.61745026759354</v>
+        <v>49.35207036711381</v>
       </c>
       <c r="G8" t="n">
         <v>700</v>
       </c>
       <c r="H8" t="n">
-        <v>6855.162803450422</v>
+        <v>6732.084661052119</v>
       </c>
       <c r="I8" t="n">
-        <v>83.61745026759354</v>
+        <v>49.35207036711381</v>
       </c>
       <c r="J8" t="n">
         <v>700</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>2.700000000000003</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>82</v>
+        <v>76.5</v>
       </c>
       <c r="B9" t="n">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="C9" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="E9" t="n">
-        <v>6378.550834611378</v>
+        <v>6694.733402835174</v>
       </c>
       <c r="F9" t="n">
-        <v>-306.4708530229286</v>
+        <v>-106.2271168965144</v>
       </c>
       <c r="G9" t="n">
         <v>700</v>
       </c>
       <c r="H9" t="n">
-        <v>6435.333459803085</v>
+        <v>6738.154240512373</v>
       </c>
       <c r="I9" t="n">
-        <v>97.55851902363213</v>
+        <v>74.63368829745343</v>
       </c>
       <c r="J9" t="n">
-        <v>655.9</v>
+        <v>688.975</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>2.700000000000003</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>76</v>
+        <v>76.5</v>
       </c>
       <c r="B10" t="n">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E10" t="n">
-        <v>6766.408565259747</v>
+        <v>6723.680627953307</v>
       </c>
       <c r="F10" t="n">
-        <v>73.89686084235655</v>
+        <v>14.34675323279771</v>
       </c>
       <c r="G10" t="n">
         <v>700</v>
       </c>
       <c r="H10" t="n">
-        <v>6766.408565259747</v>
+        <v>6738.154240512373</v>
       </c>
       <c r="I10" t="n">
-        <v>73.89686084235655</v>
+        <v>74.63368829745366</v>
       </c>
       <c r="J10" t="n">
-        <v>700</v>
+        <v>698.775</v>
       </c>
       <c r="K10" t="n">
-        <v>2.999999999999996</v>
+        <v>2.699999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>76</v>
+        <v>121.5</v>
       </c>
       <c r="B11" t="n">
         <v>124</v>
       </c>
       <c r="C11" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5</v>
+        <v>7.5</v>
       </c>
       <c r="E11" t="n">
-        <v>6749.95787635897</v>
+        <v>4574.623915454891</v>
       </c>
       <c r="F11" t="n">
-        <v>7.916751455589292</v>
+        <v>-673.9976316420361</v>
       </c>
       <c r="G11" t="n">
         <v>700</v>
       </c>
       <c r="H11" t="n">
-        <v>6764.957033886149</v>
+        <v>4088.700250269059</v>
       </c>
       <c r="I11" t="n">
-        <v>68.07508648470107</v>
+        <v>118.9577212072697</v>
       </c>
       <c r="J11" t="n">
-        <v>698.775</v>
+        <v>424.375</v>
       </c>
       <c r="K11" t="n">
-        <v>2.900000000000002</v>
+        <v>2.600000000000001</v>
       </c>
     </row>
   </sheetData>
